--- a/FishBase/fishbase mappings.xlsx
+++ b/FishBase/fishbase mappings.xlsx
@@ -23,7 +23,16 @@
     <t>habitat</t>
   </si>
   <si>
-    <t>http://eol.org/schema/terms/Habitat</t>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <u val="single"/>
+        <sz val="12"/>
+        <color indexed="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>http://purl.obolibrary.org/obo/RO_0002303</t>
+    </r>
   </si>
   <si>
     <t>freshwater</t>
@@ -150,7 +159,7 @@
       <rPr>
         <u val="single"/>
         <sz val="12"/>
-        <color indexed="12"/>
+        <color indexed="11"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>http://rs.tdwg.org/dwc/terms/verbatimDepth</t>
@@ -167,7 +176,7 @@
       <rPr>
         <u val="single"/>
         <sz val="12"/>
-        <color indexed="12"/>
+        <color indexed="11"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>http://semanticscience.org/resource/SIO_001113</t>
@@ -181,7 +190,7 @@
       <rPr>
         <u val="single"/>
         <sz val="12"/>
-        <color indexed="12"/>
+        <color indexed="11"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>http://semanticscience.org/resource/SIO_001114</t>
@@ -195,7 +204,7 @@
       <rPr>
         <u val="single"/>
         <sz val="12"/>
-        <color indexed="12"/>
+        <color indexed="11"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>http://purl.obolibrary.org/obo/UO_0000008</t>
@@ -212,7 +221,7 @@
       <rPr>
         <u val="single"/>
         <sz val="12"/>
-        <color indexed="12"/>
+        <color indexed="11"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>http://eol.org/schema/terms/pH</t>
@@ -387,7 +396,25 @@
     <t>Environment</t>
   </si>
   <si>
-    <t>MeasurementValue for http://eol.org/schema/terms/Habitat</t>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">MeasurementValue for </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <u val="single"/>
+        <sz val="12"/>
+        <color indexed="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>http://purl.obolibrary.org/obo/RO_0002303</t>
+    </r>
   </si>
   <si>
     <t>http://rs.tdwg.org/dwc/terms/measurementRemarks</t>
@@ -490,7 +517,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color indexed="8"/>
@@ -499,7 +526,7 @@
     <font>
       <sz val="12"/>
       <color indexed="8"/>
-      <name val="Helvetica"/>
+      <name val="Helvetica Neue"/>
     </font>
     <font>
       <sz val="15"/>
@@ -513,14 +540,21 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b val="1"/>
+      <u val="single"/>
       <sz val="12"/>
       <color indexed="11"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color indexed="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <u val="single"/>
       <sz val="12"/>
-      <color indexed="12"/>
+      <color indexed="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -537,7 +571,7 @@
     <font>
       <u val="single"/>
       <sz val="11"/>
-      <color indexed="12"/>
+      <color indexed="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -614,7 +648,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -627,43 +661,40 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
@@ -672,37 +703,31 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -724,8 +749,8 @@
       <rgbColor rgb="ff000000"/>
       <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="ff0000ff"/>
       <rgbColor rgb="ff333333"/>
-      <rgbColor rgb="ff0000ff"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -774,14 +799,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office Theme">
       <a:majorFont>
-        <a:latin typeface="Helvetica"/>
-        <a:ea typeface="Helvetica"/>
-        <a:cs typeface="Helvetica"/>
+        <a:latin typeface="Helvetica Neue"/>
+        <a:ea typeface="Helvetica Neue"/>
+        <a:cs typeface="Helvetica Neue"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Helvetica"/>
-        <a:ea typeface="Helvetica"/>
-        <a:cs typeface="Helvetica"/>
+        <a:latin typeface="Helvetica Neue"/>
+        <a:ea typeface="Helvetica Neue"/>
+        <a:cs typeface="Helvetica Neue"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office Theme">
@@ -876,9 +901,9 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -958,7 +983,7 @@
         </a:effectLst>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -976,7 +1001,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -986,10 +1010,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="Helvetica"/>
+            <a:ea typeface="Helvetica"/>
+            <a:cs typeface="Helvetica"/>
+            <a:sym typeface="Helvetica"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1006,7 +1030,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1032,7 +1055,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1058,7 +1080,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1084,7 +1105,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1110,7 +1130,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1136,7 +1155,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1162,7 +1180,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1188,7 +1205,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1214,7 +1230,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1245,9 +1260,9 @@
           <a:round/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
             <a:srgbClr val="000000">
-              <a:alpha val="38000"/>
+              <a:alpha val="35000"/>
             </a:srgbClr>
           </a:outerShdw>
         </a:effectLst>
@@ -1271,7 +1286,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1297,7 +1311,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1323,7 +1336,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1349,7 +1361,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1375,7 +1386,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1401,7 +1411,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1427,7 +1436,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1453,7 +1461,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1479,7 +1486,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1505,7 +1511,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1535,7 +1540,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1553,7 +1558,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1563,10 +1567,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="Helvetica"/>
+            <a:ea typeface="Helvetica"/>
+            <a:cs typeface="Helvetica"/>
+            <a:sym typeface="Helvetica"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1583,7 +1587,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1609,7 +1612,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1635,7 +1637,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1661,7 +1662,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1687,7 +1687,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1713,7 +1712,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1739,7 +1737,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1765,7 +1762,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1791,7 +1787,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1818,21 +1813,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:L81"/>
-  <sheetFormatPr defaultColWidth="10.7143" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.6667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="32.7344" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32.8516" style="1" customWidth="1"/>
     <col min="2" max="2" width="99" style="1" customWidth="1"/>
     <col min="3" max="3" width="27" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.8672" style="1" customWidth="1"/>
-    <col min="5" max="5" width="35.2891" style="1" customWidth="1"/>
-    <col min="6" max="6" width="41.7344" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.1562" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.8672" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.8672" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.8672" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.8672" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.8672" style="1" customWidth="1"/>
-    <col min="13" max="256" width="10.7344" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.8516" style="1" customWidth="1"/>
+    <col min="5" max="5" width="35.3516" style="1" customWidth="1"/>
+    <col min="6" max="6" width="41.8516" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.1719" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.8516" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.6719" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
@@ -1882,7 +1873,7 @@
       <c r="D3" s="5"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
-      <c r="G3" s="10"/>
+      <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
@@ -1900,7 +1891,7 @@
       <c r="D4" s="5"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
-      <c r="G4" s="10"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
@@ -1918,7 +1909,7 @@
       <c r="D5" s="5"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
-      <c r="G5" s="10"/>
+      <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
@@ -1932,11 +1923,11 @@
       <c r="B6" t="s" s="8">
         <v>11</v>
       </c>
-      <c r="C6" s="11"/>
+      <c r="C6" s="10"/>
       <c r="D6" s="5"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
-      <c r="G6" s="10"/>
+      <c r="G6" s="6"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
@@ -1950,7 +1941,7 @@
       <c r="B7" t="s" s="8">
         <v>11</v>
       </c>
-      <c r="C7" s="11"/>
+      <c r="C7" s="10"/>
       <c r="D7" s="5"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -1968,7 +1959,7 @@
       <c r="B8" t="s" s="8">
         <v>11</v>
       </c>
-      <c r="C8" s="11"/>
+      <c r="C8" s="10"/>
       <c r="D8" s="5"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -1986,7 +1977,7 @@
       <c r="B9" t="s" s="8">
         <v>11</v>
       </c>
-      <c r="C9" s="11"/>
+      <c r="C9" s="10"/>
       <c r="D9" s="5"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
@@ -2004,7 +1995,7 @@
       <c r="B10" t="s" s="8">
         <v>9</v>
       </c>
-      <c r="C10" s="11"/>
+      <c r="C10" s="10"/>
       <c r="D10" s="5"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -2022,7 +2013,7 @@
       <c r="B11" t="s" s="8">
         <v>17</v>
       </c>
-      <c r="C11" s="11"/>
+      <c r="C11" s="10"/>
       <c r="D11" s="5"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -2040,7 +2031,7 @@
       <c r="B12" t="s" s="8">
         <v>19</v>
       </c>
-      <c r="C12" s="11"/>
+      <c r="C12" s="10"/>
       <c r="D12" s="5"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
@@ -2058,7 +2049,7 @@
       <c r="B13" t="s" s="8">
         <v>21</v>
       </c>
-      <c r="C13" s="11"/>
+      <c r="C13" s="10"/>
       <c r="D13" s="5"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -2076,7 +2067,7 @@
       <c r="B14" t="s" s="8">
         <v>23</v>
       </c>
-      <c r="C14" s="11"/>
+      <c r="C14" s="10"/>
       <c r="D14" s="5"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
@@ -2094,7 +2085,7 @@
       <c r="B15" t="s" s="8">
         <v>25</v>
       </c>
-      <c r="C15" s="11"/>
+      <c r="C15" s="10"/>
       <c r="D15" s="5"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -2112,9 +2103,9 @@
       <c r="B16" t="s" s="8">
         <v>5</v>
       </c>
-      <c r="C16" s="11"/>
+      <c r="C16" s="10"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="12"/>
+      <c r="E16" s="11"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -2130,7 +2121,7 @@
       <c r="B17" t="s" s="8">
         <v>28</v>
       </c>
-      <c r="C17" s="11"/>
+      <c r="C17" s="10"/>
       <c r="D17" s="5"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
@@ -2148,7 +2139,7 @@
       <c r="B18" t="s" s="8">
         <v>30</v>
       </c>
-      <c r="C18" s="11"/>
+      <c r="C18" s="10"/>
       <c r="D18" s="5"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
@@ -2181,7 +2172,7 @@
       <c r="A20" t="s" s="7">
         <v>33</v>
       </c>
-      <c r="B20" t="s" s="13">
+      <c r="B20" t="s" s="12">
         <v>34</v>
       </c>
       <c r="C20" s="9"/>
@@ -2196,8 +2187,8 @@
       <c r="L20" s="6"/>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="14"/>
-      <c r="B21" s="12"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="11"/>
       <c r="C21" s="9"/>
       <c r="D21" s="5"/>
       <c r="E21" s="6"/>
@@ -2282,8 +2273,8 @@
       <c r="L25" s="6"/>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="14"/>
-      <c r="B26" s="12"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="11"/>
       <c r="C26" s="9"/>
       <c r="D26" s="5"/>
       <c r="E26" s="6"/>
@@ -2299,7 +2290,7 @@
       <c r="A27" t="s" s="7">
         <v>39</v>
       </c>
-      <c r="B27" t="s" s="13">
+      <c r="B27" t="s" s="12">
         <v>40</v>
       </c>
       <c r="C27" s="9"/>
@@ -2317,7 +2308,7 @@
       <c r="A28" t="s" s="7">
         <v>41</v>
       </c>
-      <c r="B28" t="s" s="13">
+      <c r="B28" t="s" s="12">
         <v>42</v>
       </c>
       <c r="C28" s="9"/>
@@ -2481,9 +2472,9 @@
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="15"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="14"/>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" t="s" s="8">
@@ -2596,7 +2587,7 @@
       <c r="B44" t="s" s="8">
         <v>63</v>
       </c>
-      <c r="C44" s="16"/>
+      <c r="C44" s="15"/>
       <c r="D44" s="5"/>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
@@ -2645,7 +2636,7 @@
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="6"/>
-      <c r="B47" s="10"/>
+      <c r="B47" s="6"/>
       <c r="C47" s="9"/>
       <c r="D47" s="5"/>
       <c r="E47" s="6"/>
@@ -3131,7 +3122,7 @@
       <c r="A75" t="s" s="7">
         <v>103</v>
       </c>
-      <c r="B75" s="14"/>
+      <c r="B75" s="13"/>
       <c r="C75" s="9"/>
       <c r="D75" s="5"/>
       <c r="E75" s="6"/>
@@ -3147,7 +3138,7 @@
       <c r="A76" t="s" s="7">
         <v>104</v>
       </c>
-      <c r="B76" s="14"/>
+      <c r="B76" s="13"/>
       <c r="C76" s="9"/>
       <c r="D76" s="5"/>
       <c r="E76" s="6"/>
@@ -3181,7 +3172,7 @@
       <c r="A78" t="s" s="7">
         <v>106</v>
       </c>
-      <c r="B78" s="14"/>
+      <c r="B78" s="13"/>
       <c r="C78" s="9"/>
       <c r="D78" s="5"/>
       <c r="E78" s="6"/>
@@ -3249,22 +3240,23 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B30" r:id="rId1" location="" tooltip="" display=""/>
-    <hyperlink ref="B31" r:id="rId2" location="" tooltip="" display=""/>
-    <hyperlink ref="B32" r:id="rId3" location="" tooltip="" display=""/>
-    <hyperlink ref="B33" r:id="rId4" location="" tooltip="" display=""/>
-    <hyperlink ref="B34" r:id="rId5" location="" tooltip="" display=""/>
-    <hyperlink ref="B35" r:id="rId6" location="" tooltip="" display=""/>
-    <hyperlink ref="B37" r:id="rId7" location="" tooltip="" display=""/>
-    <hyperlink ref="B38" r:id="rId8" location="" tooltip="" display=""/>
-    <hyperlink ref="B39" r:id="rId9" location="" tooltip="" display=""/>
-    <hyperlink ref="B40" r:id="rId10" location="" tooltip="" display=""/>
-    <hyperlink ref="B46" r:id="rId11" location="" tooltip="" display=""/>
+    <hyperlink ref="B2" r:id="rId1" location="" tooltip="" display="http://purl.obolibrary.org/obo/RO_0002303"/>
+    <hyperlink ref="B30" r:id="rId2" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
+    <hyperlink ref="B31" r:id="rId3" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
+    <hyperlink ref="B32" r:id="rId4" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
+    <hyperlink ref="B33" r:id="rId5" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
+    <hyperlink ref="B34" r:id="rId6" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
+    <hyperlink ref="B35" r:id="rId7" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
+    <hyperlink ref="B37" r:id="rId8" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
+    <hyperlink ref="B38" r:id="rId9" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
+    <hyperlink ref="B39" r:id="rId10" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
+    <hyperlink ref="B40" r:id="rId11" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
+    <hyperlink ref="B46" r:id="rId12" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3272,21 +3264,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:L41"/>
-  <sheetFormatPr defaultColWidth="10.7143" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.6667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="25.7344" style="17" customWidth="1"/>
-    <col min="2" max="2" width="43.2891" style="17" customWidth="1"/>
-    <col min="3" max="3" width="27" style="17" customWidth="1"/>
-    <col min="4" max="4" width="10.8672" style="17" customWidth="1"/>
-    <col min="5" max="5" width="35.2891" style="17" customWidth="1"/>
-    <col min="6" max="6" width="41.7344" style="17" customWidth="1"/>
-    <col min="7" max="7" width="20.1562" style="17" customWidth="1"/>
-    <col min="8" max="8" width="10.7344" style="17" customWidth="1"/>
-    <col min="9" max="9" width="10.7344" style="17" customWidth="1"/>
-    <col min="10" max="10" width="10.7344" style="17" customWidth="1"/>
-    <col min="11" max="11" width="10.7344" style="17" customWidth="1"/>
-    <col min="12" max="12" width="10.7344" style="17" customWidth="1"/>
-    <col min="13" max="256" width="10.7344" style="17" customWidth="1"/>
+    <col min="1" max="1" width="25.8516" style="16" customWidth="1"/>
+    <col min="2" max="2" width="43.3516" style="16" customWidth="1"/>
+    <col min="3" max="3" width="27" style="16" customWidth="1"/>
+    <col min="4" max="4" width="10.8516" style="16" customWidth="1"/>
+    <col min="5" max="5" width="35.3516" style="16" customWidth="1"/>
+    <col min="6" max="6" width="41.8516" style="16" customWidth="1"/>
+    <col min="7" max="7" width="20.1719" style="16" customWidth="1"/>
+    <col min="8" max="12" width="10.8516" style="16" customWidth="1"/>
+    <col min="13" max="16384" width="10.6719" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3296,10 +3284,10 @@
       <c r="B1" t="s" s="3">
         <v>111</v>
       </c>
-      <c r="C1" t="s" s="18">
+      <c r="C1" t="s" s="17">
         <v>112</v>
       </c>
-      <c r="D1" s="19"/>
+      <c r="D1" s="18"/>
       <c r="E1" t="s" s="2">
         <v>113</v>
       </c>
@@ -3309,11 +3297,11 @@
       <c r="G1" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="A2" t="s" s="7">
@@ -3333,11 +3321,11 @@
       <c r="G2" t="s" s="8">
         <v>79</v>
       </c>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" t="s" s="7">
@@ -3357,11 +3345,11 @@
       <c r="G3" t="s" s="8">
         <v>81</v>
       </c>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" t="s" s="7">
@@ -3381,11 +3369,11 @@
       <c r="G4" t="s" s="8">
         <v>83</v>
       </c>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" t="s" s="7">
@@ -3394,7 +3382,7 @@
       <c r="B5" t="s" s="8">
         <v>116</v>
       </c>
-      <c r="C5" t="s" s="21">
+      <c r="C5" t="s" s="19">
         <v>10</v>
       </c>
       <c r="D5" s="5"/>
@@ -3407,11 +3395,11 @@
       <c r="G5" t="s" s="8">
         <v>85</v>
       </c>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" t="s" s="7">
@@ -3420,7 +3408,7 @@
       <c r="B6" t="s" s="8">
         <v>116</v>
       </c>
-      <c r="C6" t="s" s="21">
+      <c r="C6" t="s" s="19">
         <v>12</v>
       </c>
       <c r="D6" s="5"/>
@@ -3430,12 +3418,12 @@
       <c r="F6" t="s" s="8">
         <v>36</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" t="s" s="7">
@@ -3444,7 +3432,7 @@
       <c r="B7" t="s" s="8">
         <v>116</v>
       </c>
-      <c r="C7" t="s" s="21">
+      <c r="C7" t="s" s="19">
         <v>13</v>
       </c>
       <c r="D7" s="5"/>
@@ -3454,12 +3442,12 @@
       <c r="F7" t="s" s="8">
         <v>36</v>
       </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" t="s" s="7">
@@ -3468,7 +3456,7 @@
       <c r="B8" t="s" s="8">
         <v>116</v>
       </c>
-      <c r="C8" t="s" s="21">
+      <c r="C8" t="s" s="19">
         <v>14</v>
       </c>
       <c r="D8" s="5"/>
@@ -3478,12 +3466,12 @@
       <c r="F8" t="s" s="8">
         <v>36</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" t="s" s="7">
@@ -3492,7 +3480,7 @@
       <c r="B9" t="s" s="8">
         <v>9</v>
       </c>
-      <c r="C9" t="s" s="21">
+      <c r="C9" t="s" s="19">
         <v>15</v>
       </c>
       <c r="D9" s="5"/>
@@ -3502,12 +3490,12 @@
       <c r="F9" t="s" s="8">
         <v>87</v>
       </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" t="s" s="7">
@@ -3516,7 +3504,7 @@
       <c r="B10" t="s" s="8">
         <v>17</v>
       </c>
-      <c r="C10" t="s" s="21">
+      <c r="C10" t="s" s="19">
         <v>16</v>
       </c>
       <c r="D10" s="5"/>
@@ -3526,12 +3514,12 @@
       <c r="F10" t="s" s="8">
         <v>89</v>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" t="s" s="7">
@@ -3540,16 +3528,16 @@
       <c r="B11" t="s" s="8">
         <v>19</v>
       </c>
-      <c r="C11" s="11"/>
+      <c r="C11" s="10"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" t="s" s="7">
@@ -3558,7 +3546,7 @@
       <c r="B12" t="s" s="8">
         <v>21</v>
       </c>
-      <c r="C12" s="11"/>
+      <c r="C12" s="10"/>
       <c r="D12" s="5"/>
       <c r="E12" t="s" s="2">
         <v>118</v>
@@ -3569,11 +3557,11 @@
       <c r="G12" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" t="s" s="7">
@@ -3582,7 +3570,7 @@
       <c r="B13" t="s" s="8">
         <v>23</v>
       </c>
-      <c r="C13" t="s" s="21">
+      <c r="C13" t="s" s="19">
         <v>22</v>
       </c>
       <c r="D13" s="5"/>
@@ -3592,12 +3580,12 @@
       <c r="F13" t="s" s="8">
         <v>94</v>
       </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" t="s" s="7">
@@ -3606,7 +3594,7 @@
       <c r="B14" t="s" s="8">
         <v>25</v>
       </c>
-      <c r="C14" s="11"/>
+      <c r="C14" s="10"/>
       <c r="D14" s="5"/>
       <c r="E14" t="s" s="8">
         <v>122</v>
@@ -3614,12 +3602,12 @@
       <c r="F14" t="s" s="8">
         <v>96</v>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" t="s" s="7">
@@ -3628,22 +3616,22 @@
       <c r="B15" t="s" s="8">
         <v>5</v>
       </c>
-      <c r="C15" t="s" s="21">
+      <c r="C15" t="s" s="19">
         <v>26</v>
       </c>
       <c r="D15" s="5"/>
-      <c r="E15" t="s" s="13">
+      <c r="E15" t="s" s="12">
         <v>123</v>
       </c>
-      <c r="F15" s="10"/>
+      <c r="F15" s="6"/>
       <c r="G15" t="s" s="8">
         <v>91</v>
       </c>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" t="s" s="7">
@@ -3652,7 +3640,7 @@
       <c r="B16" t="s" s="8">
         <v>28</v>
       </c>
-      <c r="C16" t="s" s="21">
+      <c r="C16" t="s" s="19">
         <v>27</v>
       </c>
       <c r="D16" s="5"/>
@@ -3665,11 +3653,11 @@
       <c r="G16" t="s" s="8">
         <v>91</v>
       </c>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" t="s" s="7">
@@ -3678,22 +3666,22 @@
       <c r="B17" t="s" s="8">
         <v>30</v>
       </c>
-      <c r="C17" t="s" s="21">
+      <c r="C17" t="s" s="19">
         <v>29</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" t="s" s="8">
         <v>88</v>
       </c>
-      <c r="F17" s="10"/>
+      <c r="F17" s="6"/>
       <c r="G17" t="s" s="8">
         <v>91</v>
       </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" t="s" s="7">
@@ -3704,50 +3692,50 @@
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="A19" t="s" s="7">
         <v>33</v>
       </c>
-      <c r="B19" t="s" s="13">
+      <c r="B19" t="s" s="12">
         <v>125</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
       <c r="C20" s="9"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
       <c r="C21" s="9"/>
       <c r="D21" s="5"/>
       <c r="E21" t="s" s="2">
@@ -3756,16 +3744,16 @@
       <c r="F21" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
       <c r="C22" s="9"/>
       <c r="D22" s="5"/>
       <c r="E22" t="s" s="7">
@@ -3774,16 +3762,16 @@
       <c r="F22" t="s" s="8">
         <v>59</v>
       </c>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
       <c r="C23" s="9"/>
       <c r="D23" s="5"/>
       <c r="E23" t="s" s="8">
@@ -3792,19 +3780,19 @@
       <c r="F23" t="s" s="8">
         <v>61</v>
       </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="20"/>
+      <c r="A24" s="6"/>
       <c r="B24" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="C24" s="22"/>
+      <c r="C24" s="9"/>
       <c r="D24" s="5"/>
       <c r="E24" t="s" s="8">
         <v>131</v>
@@ -3812,21 +3800,21 @@
       <c r="F24" t="s" s="8">
         <v>63</v>
       </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" t="s" s="7">
         <v>132</v>
       </c>
-      <c r="B25" t="s" s="13">
+      <c r="B25" t="s" s="12">
         <v>133</v>
       </c>
-      <c r="C25" s="22"/>
+      <c r="C25" s="9"/>
       <c r="D25" s="5"/>
       <c r="E25" t="s" s="8">
         <v>134</v>
@@ -3834,28 +3822,28 @@
       <c r="F25" t="s" s="8">
         <v>65</v>
       </c>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" t="s" s="7">
         <v>135</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="22"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="9"/>
       <c r="D26" s="5"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" t="s" s="7">
@@ -3864,277 +3852,278 @@
       <c r="B27" t="s" s="8">
         <v>36</v>
       </c>
-      <c r="C27" s="22"/>
+      <c r="C27" s="9"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" t="s" s="7">
         <v>41</v>
       </c>
-      <c r="B28" t="s" s="13">
+      <c r="B28" t="s" s="12">
         <v>137</v>
       </c>
-      <c r="C28" s="22"/>
+      <c r="C28" s="9"/>
       <c r="D28" s="5"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="22"/>
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="9"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="22"/>
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="9"/>
       <c r="D30" s="5"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="20"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="22"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="9"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="22"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="9"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" t="s" s="24">
+      <c r="A33" t="s" s="21">
         <v>138</v>
       </c>
-      <c r="B33" t="s" s="24">
+      <c r="B33" t="s" s="21">
         <v>43</v>
       </c>
-      <c r="C33" t="s" s="25">
+      <c r="C33" t="s" s="22">
         <v>45</v>
       </c>
       <c r="D33" s="5"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" t="s" s="27">
+      <c r="A34" t="s" s="24">
         <v>139</v>
       </c>
       <c r="B34" t="s" s="8">
         <v>44</v>
       </c>
-      <c r="C34" t="s" s="28">
+      <c r="C34" t="s" s="25">
         <v>44</v>
       </c>
       <c r="D34" s="5"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" t="s" s="27">
+      <c r="A35" t="s" s="24">
         <v>140</v>
       </c>
       <c r="B35" t="s" s="8">
         <v>47</v>
       </c>
-      <c r="C35" t="s" s="28">
+      <c r="C35" t="s" s="25">
         <v>49</v>
       </c>
       <c r="D35" s="5"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" t="s" s="27">
+      <c r="A36" t="s" s="24">
         <v>141</v>
       </c>
       <c r="B36" t="s" s="8">
         <v>51</v>
       </c>
-      <c r="C36" t="s" s="28">
+      <c r="C36" t="s" s="25">
         <v>51</v>
       </c>
       <c r="D36" s="5"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="26"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="23"/>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="20"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="22"/>
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="9"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="20"/>
-      <c r="B38" t="s" s="24">
+      <c r="A38" s="6"/>
+      <c r="B38" t="s" s="21">
         <v>53</v>
       </c>
-      <c r="C38" t="s" s="25">
+      <c r="C38" t="s" s="22">
         <v>142</v>
       </c>
       <c r="D38" s="5"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
-      <c r="L38" s="20"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
     </row>
     <row r="39" ht="17" customHeight="1">
-      <c r="A39" t="s" s="27">
+      <c r="A39" t="s" s="24">
         <v>139</v>
       </c>
       <c r="B39" t="s" s="8">
         <v>54</v>
       </c>
-      <c r="C39" t="s" s="28">
+      <c r="C39" t="s" s="25">
         <v>54</v>
       </c>
       <c r="D39" s="5"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-      <c r="K39" s="20"/>
-      <c r="L39" s="20"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
     </row>
     <row r="40" ht="17" customHeight="1">
-      <c r="A40" t="s" s="27">
+      <c r="A40" t="s" s="24">
         <v>140</v>
       </c>
       <c r="B40" t="s" s="8">
         <v>47</v>
       </c>
-      <c r="C40" t="s" s="28">
+      <c r="C40" t="s" s="25">
         <v>49</v>
       </c>
       <c r="D40" s="5"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
-      <c r="L40" s="20"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
     </row>
     <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="20"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="29"/>
+      <c r="A41" s="6"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="26"/>
       <c r="D41" s="5"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B25:B26"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B34" r:id="rId1" location="" tooltip="" display=""/>
-    <hyperlink ref="C34" r:id="rId2" location="" tooltip="" display=""/>
-    <hyperlink ref="B35" r:id="rId3" location="" tooltip="" display=""/>
-    <hyperlink ref="C35" r:id="rId4" location="" tooltip="" display=""/>
-    <hyperlink ref="B36" r:id="rId5" location="" tooltip="" display=""/>
-    <hyperlink ref="C36" r:id="rId6" location="" tooltip="" display=""/>
-    <hyperlink ref="B39" r:id="rId7" location="" tooltip="" display=""/>
-    <hyperlink ref="C39" r:id="rId8" location="" tooltip="" display=""/>
-    <hyperlink ref="B40" r:id="rId9" location="" tooltip="" display=""/>
-    <hyperlink ref="C40" r:id="rId10" location="" tooltip="" display=""/>
+    <hyperlink ref="B1" r:id="rId1" location="" tooltip="" display="http://purl.obolibrary.org/obo/RO_0002303"/>
+    <hyperlink ref="B34" r:id="rId2" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
+    <hyperlink ref="C34" r:id="rId3" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
+    <hyperlink ref="B35" r:id="rId4" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
+    <hyperlink ref="C35" r:id="rId5" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
+    <hyperlink ref="B36" r:id="rId6" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
+    <hyperlink ref="C36" r:id="rId7" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
+    <hyperlink ref="B39" r:id="rId8" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
+    <hyperlink ref="C39" r:id="rId9" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
+    <hyperlink ref="B40" r:id="rId10" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
+    <hyperlink ref="C40" r:id="rId11" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/FishBase/fishbase mappings.xlsx
+++ b/FishBase/fishbase mappings.xlsx
@@ -143,7 +143,15 @@
     <t>non-migratory (m)</t>
   </si>
   <si>
-    <t>http://www.owl-ontologies.com/unnamed.owl#Migratory</t>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="12"/>
+        <color indexed="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>http://eol.org/schema/terms/migratory</t>
+    </r>
   </si>
   <si>
     <t>non-migratory</t>
@@ -492,7 +500,31 @@
     <t>dH range</t>
   </si>
   <si>
-    <t>MeasurementType: http://www.owl-ontologies.com/unnamed.owl#Migratory, MeasurementValue: http://eol.org/schema/terms/no</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">MeasurementType: </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="12"/>
+        <color indexed="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>http://eol.org/schema/terms/migratory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>, MeasurementValue: http://eol.org/schema/terms/no</t>
+    </r>
   </si>
   <si>
     <t>OBIS STYLE TREATMENT</t>
@@ -3241,17 +3273,18 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" location="" tooltip="" display="http://purl.obolibrary.org/obo/RO_0002303"/>
-    <hyperlink ref="B30" r:id="rId2" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
-    <hyperlink ref="B31" r:id="rId3" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
-    <hyperlink ref="B32" r:id="rId4" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
-    <hyperlink ref="B33" r:id="rId5" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
-    <hyperlink ref="B34" r:id="rId6" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
-    <hyperlink ref="B35" r:id="rId7" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
-    <hyperlink ref="B37" r:id="rId8" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
-    <hyperlink ref="B38" r:id="rId9" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
-    <hyperlink ref="B39" r:id="rId10" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
-    <hyperlink ref="B40" r:id="rId11" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
-    <hyperlink ref="B46" r:id="rId12" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
+    <hyperlink ref="B27" r:id="rId2" location="" tooltip="" display="http://eol.org/schema/terms/migratory"/>
+    <hyperlink ref="B30" r:id="rId3" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
+    <hyperlink ref="B31" r:id="rId4" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
+    <hyperlink ref="B32" r:id="rId5" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
+    <hyperlink ref="B33" r:id="rId6" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
+    <hyperlink ref="B34" r:id="rId7" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
+    <hyperlink ref="B35" r:id="rId8" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
+    <hyperlink ref="B37" r:id="rId9" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
+    <hyperlink ref="B38" r:id="rId10" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
+    <hyperlink ref="B39" r:id="rId11" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
+    <hyperlink ref="B40" r:id="rId12" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
+    <hyperlink ref="B46" r:id="rId13" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
@@ -4109,16 +4142,17 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B1" r:id="rId1" location="" tooltip="" display="http://purl.obolibrary.org/obo/RO_0002303"/>
-    <hyperlink ref="B34" r:id="rId2" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
-    <hyperlink ref="C34" r:id="rId3" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
-    <hyperlink ref="B35" r:id="rId4" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
-    <hyperlink ref="C35" r:id="rId5" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
-    <hyperlink ref="B36" r:id="rId6" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
-    <hyperlink ref="C36" r:id="rId7" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
-    <hyperlink ref="B39" r:id="rId8" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
-    <hyperlink ref="C39" r:id="rId9" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
-    <hyperlink ref="B40" r:id="rId10" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
-    <hyperlink ref="C40" r:id="rId11" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
+    <hyperlink ref="B28" r:id="rId2" location="" tooltip="" display="http://eol.org/schema/terms/migratory"/>
+    <hyperlink ref="B34" r:id="rId3" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
+    <hyperlink ref="C34" r:id="rId4" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
+    <hyperlink ref="B35" r:id="rId5" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
+    <hyperlink ref="C35" r:id="rId6" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
+    <hyperlink ref="B36" r:id="rId7" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
+    <hyperlink ref="C36" r:id="rId8" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
+    <hyperlink ref="B39" r:id="rId9" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
+    <hyperlink ref="C39" r:id="rId10" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
+    <hyperlink ref="B40" r:id="rId11" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
+    <hyperlink ref="C40" r:id="rId12" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>

--- a/FishBase/fishbase mappings.xlsx
+++ b/FishBase/fishbase mappings.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="146">
   <si>
     <t>value</t>
   </si>
@@ -140,7 +140,7 @@
     <t>potamodromous?</t>
   </si>
   <si>
-    <t>non-migratory (m)</t>
+    <t>non-migratory (m) OBSOLETE</t>
   </si>
   <si>
     <r>
@@ -150,14 +150,31 @@
         <color indexed="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>http://eol.org/schema/terms/migratory</t>
+      <t>http://www.owl-ontologies.com/unnamed.owl#MigratoryStatus</t>
     </r>
   </si>
   <si>
+    <t>non-migratory OBSOLETE</t>
+  </si>
+  <si>
+    <t>http://eol.org/schema/terms/no</t>
+  </si>
+  <si>
+    <t>non-migratory (m)</t>
+  </si>
+  <si>
     <t>non-migratory</t>
   </si>
   <si>
-    <t>http://eol.org/schema/terms/no</t>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="12"/>
+        <color indexed="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>http://eol.org/schema/terms/nonmigratory</t>
+    </r>
   </si>
   <si>
     <t>mindepth</t>
@@ -1844,7 +1861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr defaultColWidth="10.6667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="32.8516" style="1" customWidth="1"/>
@@ -2355,8 +2372,12 @@
       <c r="L28" s="6"/>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
+      <c r="A29" t="s" s="7">
+        <v>43</v>
+      </c>
+      <c r="B29" t="s" s="3">
+        <v>3</v>
+      </c>
       <c r="C29" s="9"/>
       <c r="D29" s="5"/>
       <c r="E29" s="6"/>
@@ -2369,11 +2390,11 @@
       <c r="L29" s="6"/>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" t="s" s="8">
-        <v>43</v>
-      </c>
-      <c r="B30" t="s" s="8">
+      <c r="A30" t="s" s="7">
         <v>44</v>
+      </c>
+      <c r="B30" t="s" s="12">
+        <v>45</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="5"/>
@@ -2387,12 +2408,8 @@
       <c r="L30" s="6"/>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" t="s" s="8">
-        <v>45</v>
-      </c>
-      <c r="B31" t="s" s="8">
-        <v>44</v>
-      </c>
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
       <c r="C31" s="9"/>
       <c r="D31" s="5"/>
       <c r="E31" s="6"/>
@@ -2427,7 +2444,7 @@
         <v>48</v>
       </c>
       <c r="B33" t="s" s="8">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="5"/>
@@ -2442,10 +2459,10 @@
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" t="s" s="8">
+        <v>49</v>
+      </c>
+      <c r="B34" t="s" s="8">
         <v>50</v>
-      </c>
-      <c r="B34" t="s" s="8">
-        <v>51</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="5"/>
@@ -2460,10 +2477,10 @@
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" t="s" s="8">
+        <v>51</v>
+      </c>
+      <c r="B35" t="s" s="8">
         <v>52</v>
-      </c>
-      <c r="B35" t="s" s="8">
-        <v>51</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="5"/>
@@ -2477,8 +2494,12 @@
       <c r="L35" s="6"/>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
+      <c r="A36" t="s" s="8">
+        <v>53</v>
+      </c>
+      <c r="B36" t="s" s="8">
+        <v>54</v>
+      </c>
       <c r="C36" s="9"/>
       <c r="D36" s="5"/>
       <c r="E36" s="6"/>
@@ -2492,7 +2513,7 @@
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" t="s" s="8">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B37" t="s" s="8">
         <v>54</v>
@@ -2506,15 +2527,11 @@
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
-      <c r="L37" s="14"/>
+      <c r="L37" s="6"/>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" t="s" s="8">
-        <v>55</v>
-      </c>
-      <c r="B38" t="s" s="8">
-        <v>54</v>
-      </c>
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
       <c r="C38" s="9"/>
       <c r="D38" s="5"/>
       <c r="E38" s="6"/>
@@ -2531,7 +2548,7 @@
         <v>56</v>
       </c>
       <c r="B39" t="s" s="8">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="5"/>
@@ -2542,14 +2559,14 @@
       <c r="I39" s="6"/>
       <c r="J39" s="6"/>
       <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
+      <c r="L39" s="14"/>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" t="s" s="8">
+        <v>58</v>
+      </c>
+      <c r="B40" t="s" s="8">
         <v>57</v>
-      </c>
-      <c r="B40" t="s" s="8">
-        <v>49</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="5"/>
@@ -2563,8 +2580,12 @@
       <c r="L40" s="6"/>
     </row>
     <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
+      <c r="A41" t="s" s="8">
+        <v>59</v>
+      </c>
+      <c r="B41" t="s" s="8">
+        <v>50</v>
+      </c>
       <c r="C41" s="9"/>
       <c r="D41" s="5"/>
       <c r="E41" s="6"/>
@@ -2577,11 +2598,11 @@
       <c r="L41" s="6"/>
     </row>
     <row r="42" ht="17" customHeight="1">
-      <c r="A42" t="s" s="7">
-        <v>58</v>
+      <c r="A42" t="s" s="8">
+        <v>60</v>
       </c>
       <c r="B42" t="s" s="8">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="5"/>
@@ -2595,12 +2616,8 @@
       <c r="L42" s="6"/>
     </row>
     <row r="43" ht="17" customHeight="1">
-      <c r="A43" t="s" s="8">
-        <v>60</v>
-      </c>
-      <c r="B43" t="s" s="8">
-        <v>61</v>
-      </c>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
       <c r="C43" s="9"/>
       <c r="D43" s="5"/>
       <c r="E43" s="6"/>
@@ -2613,13 +2630,13 @@
       <c r="L43" s="6"/>
     </row>
     <row r="44" ht="17" customHeight="1">
-      <c r="A44" t="s" s="8">
+      <c r="A44" t="s" s="7">
+        <v>61</v>
+      </c>
+      <c r="B44" t="s" s="8">
         <v>62</v>
       </c>
-      <c r="B44" t="s" s="8">
-        <v>63</v>
-      </c>
-      <c r="C44" s="15"/>
+      <c r="C44" s="9"/>
       <c r="D44" s="5"/>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
@@ -2632,10 +2649,10 @@
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" t="s" s="8">
+        <v>63</v>
+      </c>
+      <c r="B45" t="s" s="8">
         <v>64</v>
-      </c>
-      <c r="B45" t="s" s="8">
-        <v>65</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="5"/>
@@ -2650,12 +2667,12 @@
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" t="s" s="8">
+        <v>65</v>
+      </c>
+      <c r="B46" t="s" s="8">
         <v>66</v>
       </c>
-      <c r="B46" t="s" s="8">
-        <v>51</v>
-      </c>
-      <c r="C46" s="9"/>
+      <c r="C46" s="15"/>
       <c r="D46" s="5"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
@@ -2667,8 +2684,12 @@
       <c r="L46" s="6"/>
     </row>
     <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
+      <c r="A47" t="s" s="8">
+        <v>67</v>
+      </c>
+      <c r="B47" t="s" s="8">
+        <v>68</v>
+      </c>
       <c r="C47" s="9"/>
       <c r="D47" s="5"/>
       <c r="E47" s="6"/>
@@ -2682,10 +2703,10 @@
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" t="s" s="8">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B48" t="s" s="8">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="5"/>
@@ -2699,12 +2720,8 @@
       <c r="L48" s="6"/>
     </row>
     <row r="49" ht="17" customHeight="1">
-      <c r="A49" t="s" s="8">
-        <v>69</v>
-      </c>
-      <c r="B49" t="s" s="8">
-        <v>70</v>
-      </c>
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
       <c r="C49" s="9"/>
       <c r="D49" s="5"/>
       <c r="E49" s="6"/>
@@ -2718,10 +2735,10 @@
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" t="s" s="8">
+        <v>70</v>
+      </c>
+      <c r="B50" t="s" s="8">
         <v>71</v>
-      </c>
-      <c r="B50" t="s" s="8">
-        <v>72</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="5"/>
@@ -2736,10 +2753,10 @@
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" t="s" s="8">
+        <v>72</v>
+      </c>
+      <c r="B51" t="s" s="8">
         <v>73</v>
-      </c>
-      <c r="B51" t="s" s="8">
-        <v>74</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="5"/>
@@ -2754,10 +2771,10 @@
     </row>
     <row r="52" ht="17" customHeight="1">
       <c r="A52" t="s" s="8">
+        <v>74</v>
+      </c>
+      <c r="B52" t="s" s="8">
         <v>75</v>
-      </c>
-      <c r="B52" t="s" s="8">
-        <v>36</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="5"/>
@@ -2775,7 +2792,7 @@
         <v>76</v>
       </c>
       <c r="B53" t="s" s="8">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="5"/>
@@ -2790,7 +2807,7 @@
     </row>
     <row r="54" ht="17" customHeight="1">
       <c r="A54" t="s" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B54" t="s" s="8">
         <v>36</v>
@@ -2807,8 +2824,12 @@
       <c r="L54" s="6"/>
     </row>
     <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
+      <c r="A55" t="s" s="8">
+        <v>79</v>
+      </c>
+      <c r="B55" t="s" s="8">
+        <v>36</v>
+      </c>
       <c r="C55" s="9"/>
       <c r="D55" s="5"/>
       <c r="E55" s="6"/>
@@ -2822,10 +2843,10 @@
     </row>
     <row r="56" ht="17" customHeight="1">
       <c r="A56" t="s" s="8">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B56" t="s" s="8">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="5"/>
@@ -2839,12 +2860,8 @@
       <c r="L56" s="6"/>
     </row>
     <row r="57" ht="17" customHeight="1">
-      <c r="A57" t="s" s="8">
-        <v>80</v>
-      </c>
-      <c r="B57" t="s" s="8">
-        <v>81</v>
-      </c>
+      <c r="A57" s="6"/>
+      <c r="B57" s="6"/>
       <c r="C57" s="9"/>
       <c r="D57" s="5"/>
       <c r="E57" s="6"/>
@@ -2858,10 +2875,10 @@
     </row>
     <row r="58" ht="17" customHeight="1">
       <c r="A58" t="s" s="8">
+        <v>81</v>
+      </c>
+      <c r="B58" t="s" s="8">
         <v>82</v>
-      </c>
-      <c r="B58" t="s" s="8">
-        <v>83</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="5"/>
@@ -2876,10 +2893,10 @@
     </row>
     <row r="59" ht="17" customHeight="1">
       <c r="A59" t="s" s="8">
+        <v>83</v>
+      </c>
+      <c r="B59" t="s" s="8">
         <v>84</v>
-      </c>
-      <c r="B59" t="s" s="8">
-        <v>85</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="5"/>
@@ -2893,8 +2910,12 @@
       <c r="L59" s="6"/>
     </row>
     <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
+      <c r="A60" t="s" s="8">
+        <v>85</v>
+      </c>
+      <c r="B60" t="s" s="8">
+        <v>86</v>
+      </c>
       <c r="C60" s="9"/>
       <c r="D60" s="5"/>
       <c r="E60" s="6"/>
@@ -2908,10 +2929,10 @@
     </row>
     <row r="61" ht="17" customHeight="1">
       <c r="A61" t="s" s="8">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B61" t="s" s="8">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="5"/>
@@ -2925,12 +2946,8 @@
       <c r="L61" s="6"/>
     </row>
     <row r="62" ht="17" customHeight="1">
-      <c r="A62" t="s" s="8">
-        <v>88</v>
-      </c>
-      <c r="B62" t="s" s="8">
-        <v>89</v>
-      </c>
+      <c r="A62" s="6"/>
+      <c r="B62" s="6"/>
       <c r="C62" s="9"/>
       <c r="D62" s="5"/>
       <c r="E62" s="6"/>
@@ -2944,10 +2961,10 @@
     </row>
     <row r="63" ht="17" customHeight="1">
       <c r="A63" t="s" s="8">
+        <v>89</v>
+      </c>
+      <c r="B63" t="s" s="8">
         <v>90</v>
-      </c>
-      <c r="B63" t="s" s="8">
-        <v>91</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="5"/>
@@ -2962,10 +2979,10 @@
     </row>
     <row r="64" ht="17" customHeight="1">
       <c r="A64" t="s" s="8">
+        <v>91</v>
+      </c>
+      <c r="B64" t="s" s="8">
         <v>92</v>
-      </c>
-      <c r="B64" t="s" s="8">
-        <v>91</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="5"/>
@@ -3001,7 +3018,7 @@
         <v>95</v>
       </c>
       <c r="B66" t="s" s="8">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="5"/>
@@ -3015,8 +3032,12 @@
       <c r="L66" s="6"/>
     </row>
     <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
+      <c r="A67" t="s" s="8">
+        <v>96</v>
+      </c>
+      <c r="B67" t="s" s="8">
+        <v>97</v>
+      </c>
       <c r="C67" s="9"/>
       <c r="D67" s="5"/>
       <c r="E67" s="6"/>
@@ -3029,8 +3050,12 @@
       <c r="L67" s="6"/>
     </row>
     <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
+      <c r="A68" t="s" s="8">
+        <v>98</v>
+      </c>
+      <c r="B68" t="s" s="8">
+        <v>99</v>
+      </c>
       <c r="C68" s="9"/>
       <c r="D68" s="5"/>
       <c r="E68" s="6"/>
@@ -3043,12 +3068,8 @@
       <c r="L68" s="6"/>
     </row>
     <row r="69" ht="17" customHeight="1">
-      <c r="A69" t="s" s="7">
-        <v>97</v>
-      </c>
-      <c r="B69" t="s" s="7">
-        <v>10</v>
-      </c>
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
       <c r="C69" s="9"/>
       <c r="D69" s="5"/>
       <c r="E69" s="6"/>
@@ -3061,12 +3082,8 @@
       <c r="L69" s="6"/>
     </row>
     <row r="70" ht="17" customHeight="1">
-      <c r="A70" t="s" s="7">
-        <v>98</v>
-      </c>
-      <c r="B70" t="s" s="7">
-        <v>12</v>
-      </c>
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
       <c r="C70" s="9"/>
       <c r="D70" s="5"/>
       <c r="E70" s="6"/>
@@ -3080,10 +3097,10 @@
     </row>
     <row r="71" ht="17" customHeight="1">
       <c r="A71" t="s" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B71" t="s" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="5"/>
@@ -3098,10 +3115,10 @@
     </row>
     <row r="72" ht="17" customHeight="1">
       <c r="A72" t="s" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B72" t="s" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="5"/>
@@ -3116,10 +3133,10 @@
     </row>
     <row r="73" ht="17" customHeight="1">
       <c r="A73" t="s" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B73" t="s" s="7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="5"/>
@@ -3134,10 +3151,10 @@
     </row>
     <row r="74" ht="17" customHeight="1">
       <c r="A74" t="s" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B74" t="s" s="7">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="5"/>
@@ -3152,9 +3169,11 @@
     </row>
     <row r="75" ht="17" customHeight="1">
       <c r="A75" t="s" s="7">
-        <v>103</v>
-      </c>
-      <c r="B75" s="13"/>
+        <v>104</v>
+      </c>
+      <c r="B75" t="s" s="7">
+        <v>15</v>
+      </c>
       <c r="C75" s="9"/>
       <c r="D75" s="5"/>
       <c r="E75" s="6"/>
@@ -3168,9 +3187,11 @@
     </row>
     <row r="76" ht="17" customHeight="1">
       <c r="A76" t="s" s="7">
-        <v>104</v>
-      </c>
-      <c r="B76" s="13"/>
+        <v>105</v>
+      </c>
+      <c r="B76" t="s" s="7">
+        <v>16</v>
+      </c>
       <c r="C76" s="9"/>
       <c r="D76" s="5"/>
       <c r="E76" s="6"/>
@@ -3184,11 +3205,9 @@
     </row>
     <row r="77" ht="17" customHeight="1">
       <c r="A77" t="s" s="7">
-        <v>105</v>
-      </c>
-      <c r="B77" t="s" s="7">
-        <v>22</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="B77" s="13"/>
       <c r="C77" s="9"/>
       <c r="D77" s="5"/>
       <c r="E77" s="6"/>
@@ -3202,7 +3221,7 @@
     </row>
     <row r="78" ht="17" customHeight="1">
       <c r="A78" t="s" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B78" s="13"/>
       <c r="C78" s="9"/>
@@ -3218,10 +3237,10 @@
     </row>
     <row r="79" ht="17" customHeight="1">
       <c r="A79" t="s" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B79" t="s" s="7">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="5"/>
@@ -3236,11 +3255,9 @@
     </row>
     <row r="80" ht="17" customHeight="1">
       <c r="A80" t="s" s="7">
-        <v>108</v>
-      </c>
-      <c r="B80" t="s" s="7">
-        <v>27</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B80" s="13"/>
       <c r="C80" s="9"/>
       <c r="D80" s="5"/>
       <c r="E80" s="6"/>
@@ -3254,10 +3271,10 @@
     </row>
     <row r="81" ht="17" customHeight="1">
       <c r="A81" t="s" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B81" t="s" s="7">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="5"/>
@@ -3270,21 +3287,59 @@
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
     </row>
+    <row r="82" ht="17" customHeight="1">
+      <c r="A82" t="s" s="7">
+        <v>111</v>
+      </c>
+      <c r="B82" t="s" s="7">
+        <v>27</v>
+      </c>
+      <c r="C82" s="9"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="6"/>
+      <c r="L82" s="6"/>
+    </row>
+    <row r="83" ht="17" customHeight="1">
+      <c r="A83" t="s" s="7">
+        <v>112</v>
+      </c>
+      <c r="B83" t="s" s="7">
+        <v>29</v>
+      </c>
+      <c r="C83" s="9"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="6"/>
+      <c r="J83" s="6"/>
+      <c r="K83" s="6"/>
+      <c r="L83" s="6"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" location="" tooltip="" display="http://purl.obolibrary.org/obo/RO_0002303"/>
-    <hyperlink ref="B27" r:id="rId2" location="" tooltip="" display="http://eol.org/schema/terms/migratory"/>
-    <hyperlink ref="B30" r:id="rId3" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
-    <hyperlink ref="B31" r:id="rId4" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
-    <hyperlink ref="B32" r:id="rId5" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
-    <hyperlink ref="B33" r:id="rId6" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
-    <hyperlink ref="B34" r:id="rId7" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
-    <hyperlink ref="B35" r:id="rId8" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
-    <hyperlink ref="B37" r:id="rId9" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
-    <hyperlink ref="B38" r:id="rId10" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
-    <hyperlink ref="B39" r:id="rId11" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
-    <hyperlink ref="B40" r:id="rId12" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
-    <hyperlink ref="B46" r:id="rId13" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
+    <hyperlink ref="B27" r:id="rId2" location="" tooltip="" display="http://www.owl-ontologies.com/unnamed.owl#MigratoryStatus"/>
+    <hyperlink ref="B29" r:id="rId3" location="" tooltip="" display="http://purl.obolibrary.org/obo/RO_0002303"/>
+    <hyperlink ref="B30" r:id="rId4" location="" tooltip="" display="http://eol.org/schema/terms/nonmigratory"/>
+    <hyperlink ref="B32" r:id="rId5" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
+    <hyperlink ref="B33" r:id="rId6" location="" tooltip="" display="http://rs.tdwg.org/dwc/terms/verbatimDepth"/>
+    <hyperlink ref="B34" r:id="rId7" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
+    <hyperlink ref="B35" r:id="rId8" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
+    <hyperlink ref="B36" r:id="rId9" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
+    <hyperlink ref="B37" r:id="rId10" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
+    <hyperlink ref="B39" r:id="rId11" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
+    <hyperlink ref="B40" r:id="rId12" location="" tooltip="" display="http://eol.org/schema/terms/pH"/>
+    <hyperlink ref="B41" r:id="rId13" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001113"/>
+    <hyperlink ref="B42" r:id="rId14" location="" tooltip="" display="http://semanticscience.org/resource/SIO_001114"/>
+    <hyperlink ref="B48" r:id="rId15" location="" tooltip="" display="http://purl.obolibrary.org/obo/UO_0000008"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
@@ -3300,7 +3355,7 @@
   <sheetFormatPr defaultColWidth="10.6667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="25.8516" style="16" customWidth="1"/>
-    <col min="2" max="2" width="43.3516" style="16" customWidth="1"/>
+    <col min="2" max="2" width="89.3984" style="16" customWidth="1"/>
     <col min="3" max="3" width="27" style="16" customWidth="1"/>
     <col min="4" max="4" width="10.8516" style="16" customWidth="1"/>
     <col min="5" max="5" width="35.3516" style="16" customWidth="1"/>
@@ -3312,23 +3367,23 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C1" t="s" s="17">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D1" s="18"/>
       <c r="E1" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F1" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G1" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -3346,13 +3401,13 @@
       <c r="C2" s="9"/>
       <c r="D2" s="5"/>
       <c r="E2" t="s" s="8">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s" s="8">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G2" t="s" s="8">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -3370,13 +3425,13 @@
       <c r="C3" s="9"/>
       <c r="D3" s="5"/>
       <c r="E3" t="s" s="8">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F3" t="s" s="8">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s" s="8">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -3394,13 +3449,13 @@
       <c r="C4" s="9"/>
       <c r="D4" s="5"/>
       <c r="E4" t="s" s="8">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F4" t="s" s="8">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G4" t="s" s="8">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -3413,20 +3468,20 @@
         <v>10</v>
       </c>
       <c r="B5" t="s" s="8">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s" s="19">
         <v>10</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" t="s" s="8">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F5" t="s" s="8">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="8">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
@@ -3439,14 +3494,14 @@
         <v>12</v>
       </c>
       <c r="B6" t="s" s="8">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s" s="19">
         <v>12</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" t="s" s="8">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F6" t="s" s="8">
         <v>36</v>
@@ -3463,14 +3518,14 @@
         <v>13</v>
       </c>
       <c r="B7" t="s" s="8">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C7" t="s" s="19">
         <v>13</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" t="s" s="8">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F7" t="s" s="8">
         <v>36</v>
@@ -3487,14 +3542,14 @@
         <v>14</v>
       </c>
       <c r="B8" t="s" s="8">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s" s="19">
         <v>14</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" t="s" s="8">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F8" t="s" s="8">
         <v>36</v>
@@ -3518,10 +3573,10 @@
       </c>
       <c r="D9" s="5"/>
       <c r="E9" t="s" s="8">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F9" t="s" s="8">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
@@ -3542,10 +3597,10 @@
       </c>
       <c r="D10" s="5"/>
       <c r="E10" t="s" s="8">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s" s="8">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
@@ -3582,13 +3637,13 @@
       <c r="C12" s="10"/>
       <c r="D12" s="5"/>
       <c r="E12" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
@@ -3608,10 +3663,10 @@
       </c>
       <c r="D13" s="5"/>
       <c r="E13" t="s" s="8">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F13" t="s" s="8">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -3630,10 +3685,10 @@
       <c r="C14" s="10"/>
       <c r="D14" s="5"/>
       <c r="E14" t="s" s="8">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F14" t="s" s="8">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -3654,11 +3709,11 @@
       </c>
       <c r="D15" s="5"/>
       <c r="E15" t="s" s="12">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" t="s" s="8">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
@@ -3678,13 +3733,13 @@
       </c>
       <c r="D16" s="5"/>
       <c r="E16" t="s" s="8">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F16" t="s" s="8">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G16" t="s" s="8">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
@@ -3704,11 +3759,11 @@
       </c>
       <c r="D17" s="5"/>
       <c r="E17" t="s" s="8">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" t="s" s="8">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
@@ -3739,7 +3794,7 @@
         <v>33</v>
       </c>
       <c r="B19" t="s" s="12">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="5"/>
@@ -3772,10 +3827,10 @@
       <c r="C21" s="9"/>
       <c r="D21" s="5"/>
       <c r="E21" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -3790,10 +3845,10 @@
       <c r="C22" s="9"/>
       <c r="D22" s="5"/>
       <c r="E22" t="s" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F22" t="s" s="8">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -3808,10 +3863,10 @@
       <c r="C23" s="9"/>
       <c r="D23" s="5"/>
       <c r="E23" t="s" s="8">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F23" t="s" s="8">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -3823,15 +3878,15 @@
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="6"/>
       <c r="B24" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="5"/>
       <c r="E24" t="s" s="8">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F24" t="s" s="8">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -3842,18 +3897,18 @@
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" t="s" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B25" t="s" s="12">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="5"/>
       <c r="E25" t="s" s="8">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F25" t="s" s="8">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -3864,7 +3919,7 @@
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" t="s" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="9"/>
@@ -3880,7 +3935,7 @@
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" t="s" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B27" t="s" s="8">
         <v>36</v>
@@ -3898,10 +3953,10 @@
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" t="s" s="7">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s" s="12">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="5"/>
@@ -3972,13 +4027,13 @@
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" t="s" s="21">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B33" t="s" s="21">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s" s="22">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="6"/>
@@ -3992,13 +4047,13 @@
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" t="s" s="24">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B34" t="s" s="8">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s" s="25">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="6"/>
@@ -4012,13 +4067,13 @@
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" t="s" s="24">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B35" t="s" s="8">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s" s="25">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="6"/>
@@ -4032,13 +4087,13 @@
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" t="s" s="24">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B36" t="s" s="8">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s" s="25">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="6"/>
@@ -4067,10 +4122,10 @@
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="6"/>
       <c r="B38" t="s" s="21">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s" s="22">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="6"/>
@@ -4084,13 +4139,13 @@
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" t="s" s="24">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B39" t="s" s="8">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s" s="25">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="6"/>
@@ -4104,13 +4159,13 @@
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" t="s" s="24">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B40" t="s" s="8">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C40" t="s" s="25">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="6"/>

--- a/FishBase/fishbase mappings.xlsx
+++ b/FishBase/fishbase mappings.xlsx
@@ -50,13 +50,13 @@
     <t>marine</t>
   </si>
   <si>
-    <t>http://purl.obolibrary.org/obo/ENVO_01000321</t>
+    <t>http://purl.obolibrary.org/obo/ENVO_01000307</t>
   </si>
   <si>
     <t>catadromous</t>
   </si>
   <si>
-    <t>http://purl.obolibrary.org/obo/ENVO_01000306, http://purl.obolibrary.org/obo/ENVO_01000321</t>
+    <t>http://purl.obolibrary.org/obo/ENVO_01000306, http://purl.obolibrary.org/obo/ENVO_01000307</t>
   </si>
   <si>
     <t>anadromous</t>
@@ -125,7 +125,7 @@
     <t>oceano-estuarine</t>
   </si>
   <si>
-    <t>http://purl.obolibrary.org/obo/ENVO_01000321, http://purl.obolibrary.org/obo/ENVO_01000020</t>
+    <t>http://purl.obolibrary.org/obo/ENVO_01000307, http://purl.obolibrary.org/obo/ENVO_01000020</t>
   </si>
   <si>
     <t>amphidromous?</t>
@@ -454,7 +454,7 @@
     <t>http://rs.tdwg.org/dwc/terms/measurementMethod</t>
   </si>
   <si>
-    <t>2 values: http://purl.obolibrary.org/obo/ENVO_01000306, http://purl.obolibrary.org/obo/ENVO_01000321</t>
+    <t>2 values: http://purl.obolibrary.org/obo/ENVO_01000306, http://purl.obolibrary.org/obo/ENVO_01000307</t>
   </si>
   <si>
     <t>any "body weight" measure</t>
@@ -481,7 +481,7 @@
     <t>max. published weight for female</t>
   </si>
   <si>
-    <t>2 values: http://purl.obolibrary.org/obo/ENVO_01000321, http://purl.obolibrary.org/obo/ENVO_01000020</t>
+    <t>2 values: http://purl.obolibrary.org/obo/ENVO_01000307, http://purl.obolibrary.org/obo/ENVO_01000020</t>
   </si>
   <si>
     <t>Units</t>
